--- a/data_extactor/batch_10_fa/batch_0051_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0051_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار پذیرش، ترخیص و انتقال ADT | CareOne CareEnsure | نرم‌افزار مدیریت شکایت | Corel WordPerfect Office Suite | Customer Expressions i-Sight | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic EpicCare Inpatient Clinical System | Epic Systems | نرم‌افزار Epic Systems | FaceTime | Google Docs | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | IBM Notes | نرم‌افزار MEDITECH | Manhattan Cross Cultural Group Quality Interactions | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار ارزیابی رضایت بیمار | Pemimic Patient Relations Suite | Peminic Patient Safety &amp; Quality Suite | PracticeWorks Systems Kodak WINOMS CS | Prognosis Solutions ResolvPRM | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR | rL Solutions Feedback MonitorPro</t>
+          <t>نرم‌افزار پذیرش، ترخیص و انتقال ADT | CareOne CareEnsure | نرم‌افزار مدیریت شکایت | Corel WordPerfect Office Suite | Customer Expressions i-Sight | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic EpicCare Inpatient Clinical System | Epic Systems | نرم‌افزار Epic Systems | FaceTime | Google Docs | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | IBM Notes | نرم‌افزار MEDITECH | Manhattan Cross Cultural Group Quality Interactions | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار ارزیابی رضایت بیمار | Pemimic Patient Relations Suite | Peminic Patient Safety &amp; Quality Suite | PracticeWorks Systems Kodak WINOMS CS | Prognosis Solutions ResolvPRM | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR | rL Solutions Feedback MonitorPro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | سخن‌گفتن | تفکر انتقادی | یادگیری فعال | نگارش | پایش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | پزشکی و دندانپزشکی | جامعه‌شناسی و انسان‌شناسی | اداری | روان‌شناسی | مدیریت و سازماندهی | کامپیوتر و الکترونیک | زبان انگلیسی | آموزش و پرورش | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و انسان‌شناسی | اداری | روان‌شناسی | مدیریت و اداره | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | ایمیل | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | کار با یا مشارکت در یک گروه کاری یا تیمی | اهمیت دقیق بودن یا صحت بالا | اهمیت تکرار وظایف مشابه | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | صرف زمان به صورت نشسته | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | موقعیت‌های درگیری | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ارتباط با دیگران | ایمیل | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | کارکنان بهداشت جامعه | مصاحبه‌کنندگان واجد شرایط، برنامه‌های دولتی | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مددکاران اجتماعی مراقبت‌های بهداشتی | دستیاران پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کمک‌پرستاران | تکنسین‌های روان‌پزشکی | پرستاران ثبت‌نام شده | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>پرستاران مراقبت‌های ویژه | مددکاران اجتماعی کودک، خانواده و مدرسه | متخصصان پرستاری بالینی | مددکاران سلامت جامعه | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | متخصصان آموزش بهداشت | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مددکاران اجتماعی مراقبت‌های بهداشتی | دستیاران پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | مدیران خدمات پزشکی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کمک‌پرستاران | تکنسین‌های روانپزشکی | پرستاران ثبت‌شده | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3M Encoder | Allscripts EHR | Amazing Charts | American Medical Association CodeManager | Azalea Health Azalea EHR | نرم‌افزار صدور صورتحساب | نرم‌افزار پایگاه داده کدگذاری | ComChart EMR | سیستم‌های نمایه سازی کامپیوتری | Corel WordPerfect Office Suite | Cyber Records MediChart Express | نرم‌افزار گروه‌بندی DRG | نرم‌افزار تصویربرداری پزشکی DICOM | EHS CareRevolution | Eko | نرم‌افزار پرونده الکترونیک سلامت EMR | سیستم‌های پرونده الکترونیک سلامت EMR | Elekta METRIQ | نرم‌افزار ایمیل | سیستم آرشیو کدگذاری شده EAD | نرم‌افزار رمزگذار | EndoSoft | نرم‌افزار مدیریت موجودیت | Epic Systems | Fox Meadows Accent Data Manager | Fox Meadows ChartingPlus | Fox Meadows EncounterManager | GE Healthcare Logician | نرم‌افزار گرافیکی | Greenway Medical Technologies PrimeChart | HMS | Health Care Data HealthProbe | سیستم کدگذاری رویه مشترک مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | Holt Systems eMedRec | Hyland Software OnBase | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Lotus 1-2-3 | IBM SPSS Statistics | IDX Systems IDXtend | IDX Systems Patient Chart Tracking | Information Resource Products Clinical Coding Expert | نرم‌افزار Laserfiche | LeonardoMD Renaissance | MD Synergy Medical Appointment Scheduling | نرم‌افزار MEDITECH | MedStar Systems DrWorks | Mediasoft mediOFFICE | MedicWare EMR | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Word | Minitab | NCG Medical Systems d-Chart | NDCMedisoft | NextGen Healthcare Information Systems EMR | PCC EHR | PCC Pediatric Partner | PowerMed | Practice Partner Patient Records | Purkinje Dossier | QMSoftware Receivables Management | Qlik Tech QlikView | Quest Erwin Data Modeler | R | SAP Business Objects | SAP Crystal Reports | SAS | SOAPware EMR | STAT! Systems QD Clinical | ScanSoft Naturally Speaking | نرم‌افزار تصویربرداری Scantron | نرم‌افزار زمان‌بندی | Siemens Soarian Financials | Siemens Soarian Scheduling | SoftMed ChartLocater | SoftMed ChartRelease | SoftMed ChartReserve | نرم‌افزار تشخیص گفتار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | SynaMed EMR | Tableau | Teradata Database | VantageMed ChartKeeper | نرم‌افزار شبکه خصوصی مجازی VPN | Visionary Medical Systems Visionary OFFICE PM | نرم‌افزار دیکته صوتی | نرم‌افزار مرورگر وب | Welford Chart Notes | e-MDs topsChart | نرم‌افزار eClinicalWorks EHR | eMDs Practice Partner</t>
+          <t>3M Encoder | Allscripts EHR | Amazing Charts | American Medical Association CodeManager | Azalea Health Azalea EHR | نرم‌افزار صدور صورتحساب | نرم‌افزار پایگاه داده کدگذاری | ComChart EMR | سیستم‌های نمایه‌سازی کامپیوتری | Corel WordPerfect Office Suite | Cyber Records MediChart Express | نرم‌افزار گروه‌بندی DRG | نرم‌افزار تصویربرداری پزشکی DICOM | EHS CareRevolution | Eko | نرم‌افزار پرونده الکترونیک سلامت EMR | سیستم‌های پرونده الکترونیک سلامت EMR | Elekta METRIQ | نرم‌افزار ایمیل | سیستم آرشیو کدگذاری شده EAD | نرم‌افزار کدگذار | EndoSoft | Entity Management Software | Epic Systems | Fox Meadows Accent Data Manager | Fox Meadows ChartingPlus | Fox Meadows EncounterManager | GE Healthcare Logician | نرم‌افزار گرافیکی | Greenway Medical Technologies PrimeChart | HMS | Health Care Data HealthProbe | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | Holt Systems eMedRec | Hyland Software OnBase | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Lotus 1-2-3 | IBM SPSS Statistics | IDX Systems IDXtend | IDX Systems Patient Chart Tracking | Information Resource Products Clinical Coding Expert | نرم‌افزار Laserfiche | LeonardoMD Renaissance | MD Synergy Medical Appointment Scheduling | نرم‌افزار MEDITECH | MedStar Systems DrWorks | Mediasoft mediOFFICE | MedicWare EMR | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Windows | Microsoft Word | Minitab | NCG Medical Systems d-Chart | NDCMedisoft | NextGen Healthcare Information Systems EMR | PCC EHR | PCC Pediatric Partner | PowerMed | Practice Partner Patient Records | Purkinje Dossier | QMSoftware Receivables Management | Qlik Tech QlikView | Quest Erwin Data Modeler | R | SAP Business Objects | SAP Crystal Reports | SAS | SOAPware EMR | STAT! Systems QD Clinical | ScanSoft Naturally Speaking | نرم‌افزار تصویربرداری Scantron | نرم‌افزار زمان‌بندی | Siemens Soarian Financials | Siemens Soarian Scheduling | SoftMed ChartLocater | SoftMed ChartRelease | SoftMed ChartReserve | نرم‌افزار تشخیص گفتار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | SynaMed EMR | Tableau | Teradata Database | VantageMed ChartKeeper | نرم‌افزار شبکه خصوصی مجازی VPN | Visionary Medical Systems Visionary OFFICE PM | نرم‌افزار دیکته صوتی | نرم‌افزار مرورگر وب | Welford Chart Notes | e-MDs topsChart | نرم‌افزار eClinicalWorks EHR | eMDs Practice Partner</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن‌گفتن | نگارش | پایش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | پزشکی و دندانپزشکی | زبان انگلیسی | مدیریت و سازماندهی | خدمات مشتریان و شخصی | ریاضیات | قانون و حکومت | آموزش و پرورش</t>
+          <t>رایانه و الکترونیک | پزشکی و دندان‌پزشکی | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مشکلات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | نوآوری | توجه انتخابی | اشتراک زمانی | تجسم | حفظ‌کردن | استدلال ریاضی | سهولت در کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیمی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعداد دفعات تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | مشاوران ژنتیک | متخصصان انفورماتیک سلامت | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | مدیران خدمات پزشکی و بهداشتی | تحلیل‌گران تحقیق در عملیات | نمایندگان بیمار | پزشکان طب پیشگیری | متخصصان امور نظارتی | دستیاران آماری</t>
+          <t>مدیران خدمات اداری | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | تحلیلگران سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | مشاوران ژنتیک | متخصصان انفورماتیک سلامت | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | مدیران خدمات پزشکی و بهداشتی | تحلیل‌گران تحقیق در عملیات | نمایندگان بیمار | پزشکان طب پیشگیری | متخصصان امور نظارتی | دستیاران آماری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | پایش | سخن‌گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | اداری | زیست‌شناسی | مدیریت و سازماندهی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | اداری | زیست‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | بیان شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | بینایی نزدیک | هماهنگی چند عضو | انعطاف‌پذیری بستار | نوآوری | روانی ایده‌ها | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بینایی دور | قدرت ایستا | زبردستی انگشتان | زبردستی دستی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | بینایی نزدیک | هماهنگی چند عضو | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بینایی دور | قدرت ایستا | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیمی | ایمیل | تعداد دفعات تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | اهمیت دقیق بودن یا صحت بالا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | خارج از ساختمان، در معرض همه شرایط آب و هوایی | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | پیامد اشتباه | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سطح رقابت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف مشابه | صرف زمان به صورت ایستاده | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های درگیری | پیامدهای کاری و نتایج سایر کارکنان</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، در معرض تمام شرایط آب و هوایی | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | سطح رقابت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | صرف زمان برای ایستادن | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کایروپراکتورها | مربیان و استعداد‌یاب‌ها | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مربیان تناسب اندام گروهی | هماهنگ‌کنندگان تناسب اندام و تندرستی | پرستاران متخصص | درمانگران شغلی | دستیاران کاردرمانی | کمک‌کاردرمانگرها | متخصصان ارتوپدی و پروتز | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | کمک‌فیزیوتراپیست‌ها | فیزیوتراپیست‌ها | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | پرستاران ثبت‌نام شده | درمانگران تنفسی | پزشکان طب ورزشی | متخصصان آموزش و توسعه</t>
+          <t>کایروپراکتورها | مربیان و استعدادیاب‌ها | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مدرسان تناسب اندام گروهی | هماهنگ‌کنندگان تناسب اندام و سلامتی | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | متخصصان ارتوپدی فنی و پروتز | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | درمانگران تفریحی | پرستاران ثبت‌شده | درمانگران تنفسی | پزشکان طب ورزشی | متخصصان آموزش و توسعه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نگارش | سخن‌گفتن | تفکر انتقادی | یادگیری فعال | علوم تجربی | پایش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | روان‌شناسی | پزشکی و دندانپزشکی | درمان و مشاوره | زبان انگلیسی | خدمات مشتریان و شخصی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
+          <t>زیست‌شناسی | روان‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مشکلات | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | نوآوری | روانی ایده‌ها | توجه انتخابی</t>
+          <t>درک کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | ایمیل | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | اهمیت دقیق بودن یا صحت بالا | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | برخورد با مشتریان خارجی یا عموم مردم | تعداد دفعات تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیمی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تخصص پیشرفته | متخصصان آلرژی و ایمونولوژی | متخصصان قلب | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان پزشک خانواده | پزشکان متخصص داخلی عمومی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | جراحان اطفال | پزشکان اطفال، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان طب پیشگیری | تکنسین‌های روان‌پزشکی | روان‌پزشکان</t>
+          <t>پرستاران پیشرفته روانپزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان قلب | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پزشکان طب پیشگیری | تکنسین‌های روانپزشکی | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | نرم‌افزار مستندسازی پرستاری | نرم‌افزار زمان‌بندی بیمار | نرم‌افزار ردیابی بیمار | نرم‌افزار مستندسازی تجهیزات | نرم‌افزار ارتباطی جریان کار جراحی</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | نرم‌افزار مستندسازی پرستاری | نرم‌افزار برنامه‌ریزی نوبت بیمار | نرم‌افزار ردیابی بیمار | نرم‌افزار مستندسازی ملزومات | نرم‌افزار ارتباطی جریان کار جراحی</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن‌گفتن | درک مطلب | تفکر انتقادی | پایش | نگارش | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و شخصی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | ثبات دست و بازو | زبردستی انگشتان | بینایی نزدیک | حساسیت به مشکلات | وضوح گفتار | بیان شفاهی | درک کتبی | تشخیص رنگ بصری | تشخیص گفتار | دقت کنترل | ترتیب‌دهی اطلاعات | زبردستی دستی | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | سرعت ادراکی | هماهنگی چند عضو | حساسیت شنوایی | بیان کتبی | انعطاف‌پذیری بستار | توجه شنوایی | قدرت تنه | زمان عکس‌العمل | تجسم | انعطاف‌پذیری دسته‌بندی | سرعت بستار | حفظ‌کردن | سرعت مچ و انگشت | اشتراک زمانی | بینایی دور | قدرت ایستا</t>
+          <t>درک شفاهی | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | بیان شفاهی | درک کتبی | تشخیص رنگ بصری | تشخیص گفتار | دقت کنترل | ترتیب‌دهی اطلاعات | مهارت دستی | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | سرعت ادراکی | هماهنگی چند عضو | حساسیت شنوایی | بیان کتبی | انعطاف‌پذیری بستار | توجه شنیداری | قدرت تنه | زمان عکس‌العمل | تجسم | انعطاف‌پذیری دسته‌بندی | سرعت بستار | حفظ کردن | سرعت مچ و انگشتان | تقسیم توجه | بینایی دور | قدرت ایستا</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، محیط کنترل‌شده | نزدیکی فیزیکی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیمی | اهمیت دقیق بودن یا صحت بالا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | صرف زمان به صورت ایستاده | پیامد اشتباه | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تعیین وظایف, اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | اهمیت تکرار وظایف مشابه | تعداد دفعات تصمیم‌گیری | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض تشعشع | آزادی در تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض تابش | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنسین‌های قلب و عروق | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | تکنسین‌های آندوسکوپی | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | کمک‌پرستاران | تکنسین‌های پزشکی چشم | جراحان ارتوپدی، به جز اطفال | پیراپزشکان | جراحان اطفال | دستیاران پزشک | درمانگران تنفسی | تکنسین‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | تکنسین‌های آندوسکوپی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | کمک‌پرستاران | تکنسین‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | دستیاران پزشک | درمانگران تنفسی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن‌گفتن | علوم تجربی | پایش | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و شخصی | زبان انگلیسی | کامپیوتر و الکترونیک | مدیریت و سازماندهی | زیست‌شناسی | قانون و حکومت | آموزش و پرورش</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | زیست‌شناسی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | زبردستی انگشتان | ثبات دست و بازو | زبردستی دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم | پیامد اشتباه | اهمیت دقیق بودن یا صحت بالا | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | تعداد دفعات تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیمی | فشار زمانی | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | متخصصان مدارک پزشکی | نمایندگان بیمار | مشاوران ژنتیک | مربیان ورزشی | دستیاران جراحی | متخصصان ارتوپدی و پروتز | متخصصان سمعک | عینک‌سازان، توزیع‌کننده | پرستاران ثبت‌نام شده | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشک | فن‌آوران و تکنسین‌های سلامت، سایر موارد | پزشکان تشخیص یا درمان، سایر موارد | مدیران خدمات پزشکی و بهداشتی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | هماهنگ‌کنندگان تحقیقات بالینی | اپیدمیولوژیست‌ها | مدرسان تخصص‌های بهداشتی، پس از متوسطه</t>
+          <t>فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | متخصصان مدارک پزشکی | نمایندگان بیمار | مشاوران ژنتیک | مربیان ورزشی | دستیاران جراحی | متخصصان ارتوپدی فنی و پروتز | متخصصان سمعک | عینک‌سازان، توزیع‌کننده | پرستاران ثبت‌شده | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشک | تکنولوژیست‌ها و تکنسین‌های سلامت، همه مشاغل دیگر | سایر متخصصان تشخیص یا درمان مراقبت‌های بهداشتی | مدیران خدمات پزشکی و بهداشتی | متخصصان آموزش بهداشت | مددکاران اجتماعی مراقبت‌های بهداشتی | هماهنگ‌کنندگان تحقیقات بالینی | اپیدمیولوژیست‌ها | استادان تخصص‌های بهداشتی، پس از متوسطه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AS/400 Database | نرم‌افزار ایمیل | Epic Systems | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | Private Practice | نرم‌افزار مرورگر وب</t>
+          <t>AS/400 Database | نرم‌افزار ایمیل | Epic Systems | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | Private Practice | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | گوش دادن فعال | سخن‌گفتن | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | پزشکی و دندانپزشکی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | مدیریت و سازماندهی</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | درک کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | روانی ایده‌ها | ثبات دست و بازو | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | روانی ایده‌ها | ثبات دست و بازو | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیمی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق بودن یا صحت بالا | برخورد با مشتریان خارجی یا عموم مردم | تعداد دفعات تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامد اشتباه | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | متخصصان بیهوشی | متخصصان پرستاری بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان پزشک خانواده | پزشکان متخصص داخلی عمومی | پرستاران عملی و حرفه‌ای دارای مجوز | پزشکان طب طبیعی | پرستاران بیهوشی | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | پیراپزشکان | پزشکان اطفال، عمومی | دستیاران پزشک | روان‌پزشکان | پرستاران ثبت‌نام شده</t>
+          <t>طب‌سوزنی‌ها | پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان بیهوشی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پزشکان ناتوروپاتی | پرستاران بیهوشی | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | پارامدیک‌ها | متخصصان کودکان، عمومی | دستیاران پزشک | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | پایش | درک مطلب | نگارش | سخن‌گفتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Oral Expression | درک شفاهی | حساسیت به مشکلات | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | درک کتبی | بینایی دور | ثبات دست و بازو | اشتراک زمانی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | درک کتبی | بینایی دور | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | نزدیکی فیزیکی | اهمیت دقیق بودن یا صحت بالا | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | کار با یا مشارکت در یک گروه کاری یا تیمی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعداد دفعات تصمیم‌گیری | پیامد اشتباه | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارکنان | صرف زمان برای خم شدن یا چرخاندن بدن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | متخصصان پرستاری بالینی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان پزشک خانواده | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران متخصص | کمک‌پرستاران | درمانگران شغلی | دستیاران کاردرمانی | کمک‌کاردرمانگرها | پیراپزشکان | کمک‌یاران مراقبت شخصی | دستیاران فیزیوتراپی | کمک‌فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | پرستاران ثبت‌نام شده</t>
+          <t>پرستاران مراقبت‌های ویژه | متخصصان پرستاری بالینی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان خانواده | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران متخصص | کمک‌پرستاران | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پارامدیک‌ها | کمک‌یاران مراقبت شخصی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | پایش | تفکر انتقادی | سخن‌گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ترابری | خدمات مشتریان و شخصی | آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | حمل و نقل | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مشکلات | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | قدرت تنه | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | قدرت تنه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعداد دفعات تصمیم‌گیری | صرف زمان به صورت ایستاده | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیمی | سلامت و ایمنی سایر کارکنان | پیامد اشتباه | مکالمات تلفنی | اهمیت دقیق بودن یا صحت بالا | برخورد با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه</t>
+          <t>نزدیکی فیزیکی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | پیامد خطا | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان کودک | کارکنان بهداشت جامعه | سرپرستان خط اول کارکنان خدمات شخصی | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌یاران سلامت در منزل | پرستاران عملی و حرفه‌ای دارای مجوز | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران بچه | کمک‌پرستاران | درمانگران شغلی | دستیاران کاردرمانی | کمک‌کاردرمانگرها | دستیاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و کارکنان مراقبت از کودکان | مددکاران سلامت جامعه | سرپرستان خط اول کارگران خدمات شخصی | مددکاران اجتماعی مراقبت‌های بهداشتی | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران بچه در منزل | کمک‌پرستاران | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | کمک‌یاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | پایش | سخن‌گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و سازماندهی | زبان انگلیسی | ایمنی و امنیت عمومی | پزشکی و دندانپزشکی | آموزش و پرورش | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکلات | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | قدرت ایستا | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | قدرت ایستا | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیمی | صرف زمان برای راه رفتن یا دویدن | اهمیت دقیق بودن یا صحت بالا | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | داخل ساختمان، محیط کنترل‌شده | پیامدهای کاری و نتایج سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و در گروه‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | تعداد دفعات تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم شدن یا چرخاندن بدن</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روان‌پزشکی با تخصص پیشرفته | متخصصان پرستاری بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | کمک‌یاران سلامت در منزل | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران متخصص | دستیاران کاردرمانی | کمک‌کاردرمانگرها | خدمه بیمارستان | پیراپزشکان | دستیاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | پرستاران ثبت‌نام شده | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران متخصص | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | بهیاران | پارامدیک‌ها | کمک‌یاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | پرستاران ثبت‌شده | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0051_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0051_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و مردم‌شناسی | امور اداری و دفتری | روان‌شناسی | مدیریت و امور اداری | رایانه و الکترونیک | زبان انگلیسی | آموزش و تدریس | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | جامعه‌شناسی و انسان‌شناسی | اداری | روان‌شناسی | مدیریت و اداره | رایانه و الکترونیک | زبان انگلیسی | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران بالینی متخصص | مراقبان سلامت جامعه | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | کارشناسان آموزش سلامت | کارشناسان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مددکاران اجتماعی حوزه سلامت | دستیاران پزشک | کارشناسان مدارک پزشکی | منشی‌ها و دستیاران اداری پزشکی | مدیران خدمات بهداشتی و درمانی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | کمک‌پرستاران | تکنسین‌های روان‌پزشکی | پرستاران رسمی | مشاوران توان‌بخشی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>پرستاران مراقبت‌های حاد | مددکاران اجتماعی کودک، خانواده و مدرسه | پرستاران متخصص بالینی | رابطان سلامت و بهورزان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان آموزش بهداشت و ارتقای سلامت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مددکاران اجتماعی بخش سلامت و درمان | کمک‌پزشکان و دستیاران مطب | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | مدیران خدمات درمانی و بهداشتی | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کمک‌پرستاران | تکنسین‌های روان‌پزشکی و بهداشت روان | پرستاران | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | پزشکی و دندان‌پزشکی | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | حقوق و مقررات دولتی | آموزش و تدریس</t>
+          <t>رایانه و الکترونیک | پزشکی و دندان‌پزشکی | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | ابتکار | توجه انتخابی | تسهیم زمان | تجسم‌سازی | حافظه | استدلال ریاضی | محاسبات عددی | سرعت ادراک | انعطاف‌پذیری ساختاردهی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | پرستاران بالینی متخصص | هماهنگ‌کنندگان پژوهش‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد | مشاوران ژنتیک | کارشناسان انفورماتیک سلامت | دستیاران منابع انسانی به‌جز امور حقوق و دستمزد | تحلیل‌گران مدیریت | کارشناسان مدارک پزشکی | مدیران خدمات بهداشتی و درمانی | تحلیل‌گران تحقیق در عملیات | کارشناسان امور بیماران و پذیرش | پزشکان طب پیشگیری | کارشناسان امور نظارتی و انطباق | دستیاران آمار</t>
+          <t>مدیران خدمات اداری و پشتیبانی | تکنسین‌های بیوانفورماتیک | مدیران داده‌های بالینی | پرستاران متخصص بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | مشاوران ژنتیک | متخصصان انفورماتیک سلامت | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | مدیران خدمات درمانی و بهداشتی | تحلیل‌گران تحقیق در عملیات | کارشناسان امور بیماران و پذیرش | متخصصان پزشکی اجتماعی و طب پیشگیری | کارشناسان امور رگولاتوری و انطباق مقرراتی | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | امور اداری و دفتری | زیست‌شناسی | مدیریت و امور اداری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | اداری | زیست‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | دید نزدیک | هماهنگی اندام‌ها | انعطاف‌پذیری ساختاردهی | ابتکار | روانی ایده‌ها | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | دید دور | قدرت ایستا | چابکی انگشتان | چابکی دستی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | بینایی نزدیک | هماهنگی چند عضو | انعطاف‌پذیری بستار | اصالت | روانی ایده‌ها | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بینایی دور | قدرت ایستا | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کایروپراکتیک‌ها | مربیان و استعداد‌یابان ورزشی | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | هماهنگ‌کنندگان سلامت و آمادگی جسمانی | پرستاران پیشرفته | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | متخصصان ارتوپدی فنی و ساخت اعضای مصنوعی | پزشکان طب فیزیکی و توان‌بخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپ‌ها | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | پرستاران رسمی | درمانگران تنفسی | پزشکان متخصص طب ورزشی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>کایروپراکتورها / متخصصان درمان دستی | مربیان و استعدادیابان ورزشی | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | ارتوپدهای فنی و سازندگان اعضای مصنوعی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | پزشکان طب ورزشی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | علوم پایه | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | یادگیری فعال | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | روان‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس</t>
+          <t>زیست‌شناسی | روان‌شناسی | پزشکی و دندان‌پزشکی | درمان و مشاوره | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری ساختاردهی | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | ابتکار | روانی ایده‌ها | توجه انتخابی</t>
+          <t>درک کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روان‌پزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان قلب و عروق | نوروسایکولوژیست‌های بالینی | پرستاران بالینی متخصص | روان‌شناسان بالینی و مشاوره | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | ماماها | پرستاران پیشرفته | متخصصان زنان و زایمان | جراحان اطفال | پزشکان متخصص اطفال | پزشکان طب فیزیکی و توان‌بخشی | دستیاران پزشک | پزشکان طب پیشگیری | تکنسین‌های روان‌پزشکی | روان‌پزشکان</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | متخصصان پزشکی اجتماعی و طب پیشگیری | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | ثبات دست و بازو | چابکی انگشتان | دید نزدیک | حساسیت به مسئله | وضوح گفتار | بیان شفاهی | درک کتبی | تمایز رنگ‌ها | تشخیص گفتار | دقت کنترل | مرتب‌سازی اطلاعات | چابکی دستی | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | سرعت ادراک | هماهنگی اندام‌ها | حساسیت شنوایی | بیان کتبی | انعطاف‌پذیری ساختاردهی | توجه شنیداری | قدرت تنه | زمان واکنش | تجسم‌سازی | انعطاف‌پذیری طبقه‌بندی | سرعت درک نهایی | حافظه | سرعت مچ و انگشتان | تسهیم زمان | دید دور | قدرت ایستا</t>
+          <t>درک شفاهی | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | بیان شفاهی | درک کتبی | تشخیص رنگ بصری | تشخیص گفتار | دقت کنترل | ترتیب‌دهی اطلاعات | مهارت دستی | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | سرعت ادراکی | هماهنگی چند عضو | حساسیت شنوایی | بیان کتبی | انعطاف‌پذیری بستار | توجه شنیداری | قدرت تنه | زمان عکس‌العمل | تجسم | انعطاف‌پذیری دسته‌بندی | سرعت بستار | حفظ کردن | سرعت مچ و انگشتان | تقسیم توجه | بینایی دور | قدرت ایستا</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | تکنسین‌های قلب و عروق | پرستاران بخش مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | تکنسین‌های اندوسکوپی | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | پرستاران بیهوشی | کمک‌پرستاران | تکنسین‌های چشم‌پزشکی | متخصصان جراحی ارتوپدی | امدادگران اورژانس | جراحان اطفال | دستیاران پزشک | درمانگران تنفسی | تکنسین‌های اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | تکنسین‌های اندوسکوپی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | کمک‌پرستاران | تکنسین‌های مراقبت‌های چشمی | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | دستیاران پزشک | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | مدیریت و امور اداری | زیست‌شناسی | حقوق و مقررات دولتی | آموزش و تدریس</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | زیست‌شناسی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تجسم‌سازی | تسهیم زمان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان مدارک پزشکی | کارشناسان امور بیماران و پذیرش | مشاوران ژنتیک | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | دستیاران جراحی | متخصصان ارتوپدی فنی و ساخت اعضای مصنوعی | متخصصان شنوایی‌سنجی و سمعک | عینک‌سازان (ساخت و فروش عینک) | پرستاران رسمی | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | سایر تکنسین‌ها و کاردان‌های حوزه سلامت | سایر پزشکان و درمانگران حوزه سلامت | مدیران خدمات بهداشتی و درمانی | کارشناسان آموزش سلامت | مددکاران اجتماعی حوزه سلامت | هماهنگ‌کنندگان پژوهش‌های بالینی | اپیدمیولوژیست‌ها | مدرسان علوم پزشکی و بهداشت در آموزش عالی</t>
+          <t>کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان امور بیماران و پذیرش | مشاوران ژنتیک | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | دستیاران جراحی | ارتوپدهای فنی و سازندگان اعضای مصنوعی | کارشناسان تجویز و ساخت سمعک | عینک‌سازان (ساخت و فروش عینک) | پرستاران | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | سایر متخصصان و تکنسین‌های حوزه سلامت | سایر متخصصان تشخیص و درمان حوزه سلامت | مدیران خدمات درمانی و بهداشتی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | هماهنگ‌کنندگان کارآزمایی‌های بالینی | متخصصان همه‌گیرشناسی و اپیدمیولوژیست‌ها | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | زیست‌شناسی | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | روان‌شناسی | درمان و مشاوره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | وضوح گفتار | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | بیان کتبی | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | انعطاف‌پذیری ساختاردهی | روانی ایده‌ها | ثبات دست و بازو | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | روانی ایده‌ها | ثبات دست و بازو | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | پرستاران بخش مراقبت‌های حاد | پرستاران پیشرفته روان‌پزشکی | متخصصان بیهوشی | پرستاران بالینی متخصص | پرستاران بخش مراقبت‌های ویژه (ICU) | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | پزشکان طب سنتی و طبیعی | پرستاران بیهوشی | ماماپرستاران | پرستاران پیشرفته | متخصصان زنان و زایمان | امدادگران اورژانس | پزشکان متخصص اطفال | دستیاران پزشک | روان‌پزشکان | پرستاران رسمی</t>
+          <t>متخصصان و کارشناسان طب سوزنی | پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | متخصصان بیهوشی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | بهیاران و کمک‌پرستاران دارای مجوز | پزشکان طب طبیعی و نتوپاتی | پرستاران بیهوشی | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | متخصصان عمومی کودکان | دستیاران پزشک | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | دید نزدیک | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | درک کتبی | دید دور | ثبات دست و بازو | تسهیم زمان | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بیان کتبی | روانی ایده‌ها | درک کتبی | بینایی دور | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | پرستاران بالینی متخصص | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | پرستاران پیشرفته | کمک‌پرستاران | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | امدادگران اورژانس | مراقبان خدمات شخصی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | درمانگران تفریحی | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران متخصص بالینی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بالینی پیشرفته | کمک‌پرستاران | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | مراقبان خدمات شخصی و همراهان توان‌خواهان | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حمل‌ونقل و ترابری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | حمل و نقل | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان کتبی | قدرت تنه | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان کتبی | قدرت تنه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | مراقبان سلامت جامعه | سرپرستان رده‌اول ارائه‌دهندگان خدمات فردی | مددکاران اجتماعی حوزه سلامت | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوءمصرف مواد | پرستاران خانگی کودک | کمک‌پرستاران | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | کمک‌فیزیوتراپ‌ها | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و رفاهی | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مربیان و مراقبان کودک | رابطان سلامت و بهورزان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مددکاران اجتماعی بخش سلامت و درمان | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران خانگی و دایه‌ها | کمک‌پرستاران | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و تدریس | درمان و مشاوره</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | دید نزدیک | تشخیص گفتار | قدرت ایستا | قدرت تنه | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی | انعطاف‌پذیری بدنی | ثبات دست و بازو | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | وضوح گفتار</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | قدرت ایستا | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | وضوح گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های حاد | پرستاران پیشرفته روان‌پزشکی | پرستاران بالینی متخصص | پرستاران بخش مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | پرستاران بیهوشی | پرستاران پیشرفته | کمک‌کاردرمانگران | دستیاران کاردرمانی | متصدیان خدمات عمومی بیمارستان (خدمات) | امدادگران اورژانس | کمک‌فیزیوتراپ‌ها | بهیاران روان‌پزشکی | تکنسین‌های روان‌پزشکی | پرستاران رسمی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | پرستاران بالینی پیشرفته | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | خدمات‌دهندگان و انتقال‌دهندگان بیمار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | کمک‌یاران فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | پرستاران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
